--- a/jogos_2025-05-23.xlsx
+++ b/jogos_2025-05-23.xlsx
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,65 +1314,65 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>2.65</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>2.19</v>
       </c>
       <c r="O7" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.15</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.41</v>
-      </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['9', '45+1', '62', '65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45800.375</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="N9" t="n">
-        <v>2.19</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['4', '27', '82']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45800.375</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>4.1</v>
+        <v>5.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['9', '45+1', '62', '65']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['4', '27', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45800.375</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Inhulets</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Livyi Bereh</t>
+          <t>Vorskla</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N13" t="n">
         <v>2.18</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.88</v>
       </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.75</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.2</v>
+        <v>2.89</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45800.39583333334</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Inhulets</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vorskla</t>
+          <t>Livyi Bereh</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N14" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.8</v>
+        <v>3.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45800.39583333334</v>
@@ -3103,20 +3103,20 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['18', '21', '42', '44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,19 +3223,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>NK Bjelovar</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['49']</t>
         </is>
       </c>
       <c r="AG22" t="n">
@@ -3352,19 +3352,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NK Bjelovar</t>
+          <t>Hrvatski Dragovoljac</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,16 +3481,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hrvatski Dragovoljac</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AG24" t="n">
@@ -4374,119 +4374,119 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45800.60416666666</v>
@@ -4503,29 +4503,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['6', '63', '9002']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45800.60416666666</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.61</v>
+        <v>1.82</v>
       </c>
       <c r="M33" t="n">
-        <v>2.94</v>
+        <v>3.26</v>
       </c>
       <c r="N33" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="O33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.35</v>
       </c>
       <c r="R33" t="n">
         <v>1.38</v>
@@ -4692,25 +4692,25 @@
         <v>2.8</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V33" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>3.35</v>
@@ -4719,32 +4719,32 @@
         <v>1.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI33" t="n">
         <v>2.05</v>
       </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['25']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45800.60416666666</v>
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.82</v>
+        <v>2.47</v>
       </c>
       <c r="M34" t="n">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>3.79</v>
+        <v>2.49</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2.8</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AB34" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD34" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4860,20 +4860,20 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45800.60416666666</v>
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="M35" t="n">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="N35" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="n">
         <v>2.05</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Q35" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="R35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.3</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AC35" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45800.60416666666</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>1</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>5.2</v>
+        <v>4.09</v>
       </c>
       <c r="N38" t="n">
-        <v>6.63</v>
+        <v>4.25</v>
       </c>
       <c r="O38" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="P38" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="R38" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S38" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="T38" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="U38" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
-        <v>6.65</v>
+        <v>5.75</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>2.45</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['47']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['5']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45800.63541666666</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>FC Schaffhausen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.57</v>
+        <v>2.9</v>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>3.8</v>
+        <v>2.16</v>
       </c>
       <c r="O39" t="n">
-        <v>2.03</v>
+        <v>3.53</v>
       </c>
       <c r="P39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.41</v>
       </c>
-      <c r="Q39" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.06</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['78', '90']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '75', '90+1']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.15</v>
+        <v>1.32</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.52</v>
+        <v>2.22</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.43</v>
+        <v>1.69</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45800.63541666666</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FC Schaffhausen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>2.16</v>
+        <v>3.8</v>
       </c>
       <c r="O40" t="n">
-        <v>3.53</v>
+        <v>2.03</v>
       </c>
       <c r="P40" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.68</v>
+        <v>4.42</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="T40" t="n">
-        <v>2.41</v>
+        <v>2.06</v>
       </c>
       <c r="U40" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="Z40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['78', '90']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH40" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['15', '75', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AI40" t="n">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.69</v>
+        <v>2.43</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45800.63541666666</v>
@@ -5803,109 +5803,109 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="M42" t="n">
-        <v>4.09</v>
+        <v>5.2</v>
       </c>
       <c r="N42" t="n">
-        <v>4.25</v>
+        <v>6.63</v>
       </c>
       <c r="O42" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="P42" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S42" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="U42" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45800.63541666666</v>
@@ -5922,26 +5922,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.86</v>
+        <v>6.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="N43" t="n">
-        <v>3.35</v>
+        <v>1.42</v>
       </c>
       <c r="O43" t="n">
-        <v>2.47</v>
+        <v>5.1</v>
       </c>
       <c r="P43" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.9</v>
+        <v>2.11</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S43" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T43" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U43" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X43" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.02</v>
+        <v>2.58</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['18', '59']</t>
+          <t>['20', '51']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45800.65625</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,109 +6061,109 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
         <v>2</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
       <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="M44" t="n">
-        <v>5.4</v>
+        <v>4.12</v>
       </c>
       <c r="N44" t="n">
-        <v>8.699999999999999</v>
+        <v>5.72</v>
       </c>
       <c r="O44" t="n">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="P44" t="n">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="R44" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S44" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="U44" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V44" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X44" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AC44" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['43', '68']</t>
+          <t>['34', '40', '57']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '59']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AJ44" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45800.65625</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,23 +6190,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>1</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.87</v>
+        <v>1.33</v>
       </c>
       <c r="M45" t="n">
-        <v>3.18</v>
+        <v>5.4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>3.3</v>
+        <v>1.81</v>
       </c>
       <c r="P45" t="n">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="Q45" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['43', '68']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH45" t="n">
         <v>3.1</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X45" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AI45" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45800.65625</v>
@@ -6309,32 +6309,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
         <v>2</v>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.26</v>
+        <v>3.09</v>
       </c>
       <c r="M46" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>14</v>
+        <v>2.51</v>
       </c>
       <c r="O46" t="n">
-        <v>1.57</v>
+        <v>3.75</v>
       </c>
       <c r="P46" t="n">
-        <v>2.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q46" t="n">
-        <v>10.2</v>
+        <v>2.99</v>
       </c>
       <c r="R46" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="S46" t="n">
-        <v>3.54</v>
+        <v>2.29</v>
       </c>
       <c r="T46" t="n">
-        <v>2.25</v>
+        <v>3.55</v>
       </c>
       <c r="U46" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W46" t="n">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="X46" t="n">
-        <v>5.25</v>
+        <v>2.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.39</v>
+        <v>4.6</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['42', '51']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70', '89']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="AH46" t="n">
-        <v>4.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="AJ46" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45800.65625</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,109 +6448,109 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V47" t="n">
         <v>1</v>
       </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N47" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="O47" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.03</v>
-      </c>
       <c r="W47" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X47" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD47" t="n">
         <v>2.1</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['33', '52', '55', '64', '86']</t>
+          <t>['28', '33']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['2', '80']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.74</v>
+        <v>3.75</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45800.65625</v>
@@ -6567,26 +6567,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>2</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6.5</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>1.42</v>
+        <v>3.35</v>
       </c>
       <c r="O48" t="n">
-        <v>5.1</v>
+        <v>2.47</v>
       </c>
       <c r="P48" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.11</v>
+        <v>3.9</v>
       </c>
       <c r="R48" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="T48" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U48" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V48" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X48" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.58</v>
+        <v>3.02</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['20', '51']</t>
+          <t>['18', '59']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="AI48" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45800.65625</v>
@@ -6696,33 +6696,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>2</v>
       </c>
       <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>1</v>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N49" t="n">
+        <v>14</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X49" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD49" t="n">
         <v>1.63</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N49" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X49" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['48', '84']</t>
+          <t>['42', '51']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AJ49" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45800.65625</v>
@@ -6835,19 +6835,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.09</v>
+        <v>2.87</v>
       </c>
       <c r="M50" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X50" t="n">
         <v>3</v>
       </c>
-      <c r="N50" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Y50" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['70', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45800.65625</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,22 +7093,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
         <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>3.22</v>
       </c>
       <c r="N52" t="n">
-        <v>5.5</v>
+        <v>2.35</v>
       </c>
       <c r="O52" t="n">
-        <v>2.04</v>
+        <v>3.55</v>
       </c>
       <c r="P52" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="R52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.28</v>
       </c>
-      <c r="S52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X52" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AC52" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['28', '33']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['2', '80']</t>
+          <t>['38', '90+6']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AJ52" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45800.65625</v>
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
         <v>1</v>
       </c>
-      <c r="H53" t="n">
-        <v>2</v>
-      </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="M53" t="n">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="N53" t="n">
-        <v>2.35</v>
+        <v>4.35</v>
       </c>
       <c r="O53" t="n">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="P53" t="n">
-        <v>2.01</v>
+        <v>2.39</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.92</v>
+        <v>4.75</v>
       </c>
       <c r="R53" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S53" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="T53" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V53" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W53" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="X53" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['33', '52', '55', '64', '86']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['38', '90+6']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.06</v>
+        <v>1.47</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45800.65625</v>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="M54" t="n">
-        <v>4.12</v>
+        <v>3.65</v>
       </c>
       <c r="N54" t="n">
-        <v>5.72</v>
+        <v>5.5</v>
       </c>
       <c r="O54" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="P54" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="R54" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T54" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="U54" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V54" t="n">
         <v>1</v>
       </c>
       <c r="W54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB54" t="n">
         <v>1.25</v>
       </c>
-      <c r="X54" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC54" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['34', '40', '57']</t>
+          <t>['48', '84']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['3', '59']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AG54" t="n">
         <v>1.25</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AJ54" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45800.65625</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,19 +7480,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="M55" t="n">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="N55" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="O55" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="P55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y55" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U55" t="n">
+      <c r="Z55" t="n">
         <v>1.55</v>
       </c>
-      <c r="V55" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X55" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y55" t="n">
+      <c r="AA55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD55" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG55" t="n">
         <v>1.33</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AJ55" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45800.66666666666</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,19 +7609,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G56" t="n">
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="M56" t="n">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="N56" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="O56" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="P56" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q56" t="n">
-        <v>6.75</v>
+        <v>3.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S56" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="T56" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="U56" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="V56" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W56" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="X56" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AA56" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG56" t="n">
         <v>1.33</v>
       </c>
       <c r="AH56" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45800.66666666666</v>
@@ -8889,35 +8889,35 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.14</v>
+        <v>1.48</v>
       </c>
       <c r="M66" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="N66" t="n">
-        <v>1.96</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="P66" t="n">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.73</v>
+        <v>4.4</v>
       </c>
       <c r="R66" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S66" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="T66" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="U66" t="n">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="V66" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="X66" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="AA66" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '50', '51', '62', '64', '67']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '33', '90+1']</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AI66" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45800.875</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,25 +9028,25 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="M67" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="N67" t="n">
         <v>5</v>
       </c>
       <c r="O67" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="P67" t="n">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="R67" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="S67" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="T67" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="U67" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W67" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="X67" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.95</v>
+        <v>3.34</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AD67" t="n">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['9', '50', '51', '62', '64', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>['18', '33', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.91</v>
+        <v>2.79</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AJ67" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45800.875</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.65</v>
+        <v>4.14</v>
       </c>
       <c r="M68" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="N68" t="n">
-        <v>5</v>
+        <v>1.96</v>
       </c>
       <c r="O68" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="P68" t="n">
         <v>2.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>2.73</v>
       </c>
       <c r="R68" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S68" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="T68" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="U68" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W68" t="n">
         <v>1.33</v>
       </c>
-      <c r="V68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X68" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AA68" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,16 +9250,16 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH68" t="n">
-        <v>2.79</v>
+        <v>1.29</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AJ68" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45800.875</v>
